--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N7_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0002T0006Z000C1N7_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.61225102467801</v>
+        <v>5.136990791510176</v>
       </c>
       <c r="D2" t="n">
-        <v>31.30334919276994</v>
+        <v>5.086794243825116</v>
       </c>
       <c r="E2" t="n">
-        <v>22.88119907726369</v>
+        <v>3.71819485005535</v>
       </c>
       <c r="F2" t="n">
-        <v>22.83141867091442</v>
+        <v>3.710105534023594</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.098921149721147</v>
+        <v>1.153574686829687</v>
       </c>
       <c r="D3" t="n">
-        <v>7.302525309878747</v>
+        <v>1.186660362855296</v>
       </c>
       <c r="E3" t="n">
-        <v>22.88119907726369</v>
+        <v>3.71819485005535</v>
       </c>
       <c r="F3" t="n">
-        <v>22.83141867091442</v>
+        <v>3.710105534023594</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>62.32535779265877</v>
+        <v>10.12787064130705</v>
       </c>
       <c r="D4" t="n">
-        <v>62.06581711047131</v>
+        <v>10.08569528045159</v>
       </c>
       <c r="E4" t="n">
-        <v>22.88119907726369</v>
+        <v>3.71819485005535</v>
       </c>
       <c r="F4" t="n">
-        <v>22.83141867091442</v>
+        <v>3.710105534023594</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>69.47908616754718</v>
+        <v>11.29035150222642</v>
       </c>
       <c r="D5" t="n">
-        <v>69.28403335200757</v>
+        <v>11.25865541970123</v>
       </c>
       <c r="E5" t="n">
-        <v>22.88119907726369</v>
+        <v>3.71819485005535</v>
       </c>
       <c r="F5" t="n">
-        <v>22.83141867091442</v>
+        <v>3.710105534023594</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>80.42624760531541</v>
+        <v>13.06926523586375</v>
       </c>
       <c r="D6" t="n">
-        <v>80.47152818679724</v>
+        <v>13.07662333035455</v>
       </c>
       <c r="E6" t="n">
-        <v>22.88119907726369</v>
+        <v>3.71819485005535</v>
       </c>
       <c r="F6" t="n">
-        <v>22.83141867091442</v>
+        <v>3.710105534023594</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>55.91298552301034</v>
+        <v>9.08586014748918</v>
       </c>
       <c r="D7" t="n">
-        <v>55.91484611901026</v>
+        <v>9.086162494339169</v>
       </c>
       <c r="E7" t="n">
-        <v>22.88119907726369</v>
+        <v>3.71819485005535</v>
       </c>
       <c r="F7" t="n">
-        <v>22.83141867091442</v>
+        <v>3.710105534023594</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.66821525676025</v>
+        <v>8.558584979223541</v>
       </c>
       <c r="D8" t="n">
-        <v>52.59331425787759</v>
+        <v>8.546413566905109</v>
       </c>
       <c r="E8" t="n">
-        <v>22.88119907726369</v>
+        <v>3.71819485005535</v>
       </c>
       <c r="F8" t="n">
-        <v>22.83141867091442</v>
+        <v>3.710105534023594</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
